--- a/Angebot.xlsx
+++ b/Angebot.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA31AC74-260C-4B38-910E-290B7032A21F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1605" yWindow="1350" windowWidth="28800" windowHeight="14580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="900" windowWidth="28800" windowHeight="14580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Katalog" sheetId="1" r:id="rId1"/>
